--- a/report_modules/solar_default_source/output.xlsx
+++ b/report_modules/solar_default_source/output.xlsx
@@ -14,45 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="84">
   <si>
     <t>S.No.</t>
   </si>
   <si>
-    <t>Image Type</t>
-  </si>
-  <si>
-    <t>Block No.</t>
-  </si>
-  <si>
-    <t>String No.</t>
-  </si>
-  <si>
-    <t>Row No.</t>
-  </si>
-  <si>
-    <t>Table No.</t>
-  </si>
-  <si>
-    <t>Module No.</t>
+    <t>Mast Name</t>
   </si>
   <si>
     <t>Defect</t>
   </si>
   <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Average Temp.</t>
-  </si>
-  <si>
-    <t>Delta Temp.</t>
-  </si>
-  <si>
-    <t>Min Temp.</t>
-  </si>
-  <si>
-    <t>Max Temp.</t>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Sub-Component</t>
   </si>
   <si>
     <t>Latitude</t>
@@ -61,52 +37,235 @@
     <t>Longitude</t>
   </si>
   <si>
-    <t>Thermal Image Url</t>
-  </si>
-  <si>
-    <t>Visual Image Url</t>
-  </si>
-  <si>
-    <t>Capture Date</t>
-  </si>
-  <si>
-    <t>Remarks/Comment</t>
-  </si>
-  <si>
-    <t>FL-5</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>BROKEN MODULE</t>
-  </si>
-  <si>
-    <t>CELL MISMATCH</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>https://minio.mapbyvaayu.com/vaayudatarepo/vaayu/rawimages/Solar/surveys/848aeb63-66b7-4a2e-b075-b5fd78b80cee/FL-5/DJI_20251117140737_0001_T.JPG</t>
-  </si>
-  <si>
-    <t>https://minio.mapbyvaayu.com/vaayudatarepo/vaayu/rawimages/Solar/surveys/848aeb63-66b7-4a2e-b075-b5fd78b80cee/FL-5/DJI_20251117140738_0002_T.JPG</t>
-  </si>
-  <si>
-    <t>https://minio.mapbyvaayu.com/vaayudatarepo/vaayu/rawimages/Solar/surveys/848aeb63-66b7-4a2e-b075-b5fd78b80cee/FL-5/DJI_20251117140737_0001_V.JPG</t>
-  </si>
-  <si>
-    <t>Jan 15, 2026</t>
+    <t>Visual Image URL</t>
+  </si>
+  <si>
+    <t>615-25</t>
+  </si>
+  <si>
+    <t>615-27</t>
+  </si>
+  <si>
+    <t>615-5</t>
+  </si>
+  <si>
+    <t>615-9</t>
+  </si>
+  <si>
+    <t>616-1</t>
+  </si>
+  <si>
+    <t>616-11</t>
+  </si>
+  <si>
+    <t>616-13</t>
+  </si>
+  <si>
+    <t>616-17</t>
+  </si>
+  <si>
+    <t>616-19</t>
+  </si>
+  <si>
+    <t>616-21</t>
+  </si>
+  <si>
+    <t>616-23</t>
+  </si>
+  <si>
+    <t>616-25</t>
+  </si>
+  <si>
+    <t>616-3</t>
+  </si>
+  <si>
+    <t>616-5</t>
+  </si>
+  <si>
+    <t>616-7</t>
+  </si>
+  <si>
+    <t>616-9</t>
+  </si>
+  <si>
+    <t>617-11</t>
+  </si>
+  <si>
+    <t>617-25</t>
+  </si>
+  <si>
+    <t>617-27</t>
+  </si>
+  <si>
+    <t>617-29</t>
+  </si>
+  <si>
+    <t>617-3</t>
+  </si>
+  <si>
+    <t>617-9</t>
+  </si>
+  <si>
+    <t>618-19</t>
+  </si>
+  <si>
+    <t>618-27</t>
+  </si>
+  <si>
+    <t>618-29</t>
+  </si>
+  <si>
+    <t>618-5</t>
+  </si>
+  <si>
+    <t>618-7</t>
+  </si>
+  <si>
+    <t>618-9</t>
+  </si>
+  <si>
+    <t>equalising plate inclined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bracket assembly rusted </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number plate missing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rust </t>
+  </si>
+  <si>
+    <t>Suspension Clamp Rusted</t>
+  </si>
+  <si>
+    <t>Guy rode wire</t>
+  </si>
+  <si>
+    <t>Registration Tube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equalising plate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bracket assembly </t>
+  </si>
+  <si>
+    <t>Boards</t>
+  </si>
+  <si>
+    <t>mast</t>
+  </si>
+  <si>
+    <t>Insulator</t>
+  </si>
+  <si>
+    <t>Registration tube</t>
+  </si>
+  <si>
+    <t>Stay tube</t>
+  </si>
+  <si>
+    <t>rusted</t>
+  </si>
+  <si>
+    <t>missing</t>
+  </si>
+  <si>
+    <t>mast arm</t>
+  </si>
+  <si>
+    <t>wire rusted</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603105706_0162_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603105711_0163_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603105602_0155_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603113749_0104_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603113440_0085_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603105419_0146_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603104552_0095_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603104430_0085_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603104010_0065_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603103819_0054_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603103555_0039_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603103433_0030_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603103301_0019_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603105224_0136_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603105106_0126_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603104911_0116_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603104736_0105_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603101703_0101_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603100359_0028_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603100147_0017_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603100158_0018_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603100017_0010_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603102411_0146_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260603101834_0110_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260601185655_0062_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260601185002_0026_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260601184745_0016_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260601190854_0132_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260601190715_0122_V.JPG</t>
+  </si>
+  <si>
+    <t>https://coredatarepo.s3.ap-south-1.amazonaws.com/Yugmi/rawimages/4c6028ec-8c8a-4175-85f5-d8fa91816411/DJI_20260601190542_0111_V.JPG</t>
   </si>
 </sst>
 </file>
@@ -477,29 +636,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
-    <col min="12" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" customWidth="1"/>
-    <col min="16" max="17" width="146.7109375" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="133.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,160 +674,1197 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2">
-        <v>31.48</v>
-      </c>
-      <c r="K2">
-        <v>7.010000000000002</v>
-      </c>
-      <c r="L2">
-        <v>27.98</v>
-      </c>
-      <c r="M2">
-        <v>34.99</v>
-      </c>
-      <c r="N2">
-        <v>25.09508680555555</v>
-      </c>
-      <c r="O2">
-        <v>82.35393422222222</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>21.99808780555556</v>
+      </c>
+      <c r="G2">
+        <v>83.13964494444446</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>21.99808922222222</v>
+      </c>
+      <c r="G3">
+        <v>83.13960872222223</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4">
+        <v>21.99807913888889</v>
+      </c>
+      <c r="G4">
+        <v>83.13915072222223</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5">
+        <v>21.9978975</v>
+      </c>
+      <c r="G5">
+        <v>83.14628816666668</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>21.99800455555556</v>
+      </c>
+      <c r="G6">
+        <v>83.14497527777779</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>21.99800455555556</v>
+      </c>
+      <c r="G7">
+        <v>83.14497527777779</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>21.99805625</v>
+      </c>
+      <c r="G8">
+        <v>83.13848580555556</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>21.99805625</v>
+      </c>
+      <c r="G9">
+        <v>83.13848580555556</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>21.99790305555556</v>
+      </c>
+      <c r="G10">
+        <v>83.13497030555556</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>21.99787363888889</v>
+      </c>
+      <c r="G11">
+        <v>83.13430986111112</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>21.99787363888889</v>
+      </c>
+      <c r="G12">
+        <v>83.13430986111112</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13">
+        <v>21.99781527777778</v>
+      </c>
+      <c r="G13">
+        <v>83.13301427777778</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>21.99777686111111</v>
+      </c>
+      <c r="G14">
+        <v>83.13228022222222</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15">
+        <v>21.99777686111111</v>
+      </c>
+      <c r="G15">
+        <v>83.13228022222222</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>21.99775544444444</v>
+      </c>
+      <c r="G16">
+        <v>83.13159169444444</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17">
+        <v>21.99775544444444</v>
+      </c>
+      <c r="G17">
+        <v>83.13159169444444</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>21.99772322222222</v>
+      </c>
+      <c r="G18">
+        <v>83.13092455555555</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>21.99772322222222</v>
+      </c>
+      <c r="G19">
+        <v>83.13092455555555</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20">
+        <v>21.99770441666667</v>
+      </c>
+      <c r="G20">
+        <v>83.1302131111111</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>21.99770441666667</v>
+      </c>
+      <c r="G21">
+        <v>83.1302131111111</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>21.99801152777778</v>
+      </c>
+      <c r="G22">
+        <v>83.13770877777779</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23">
+        <v>21.99801152777778</v>
+      </c>
+      <c r="G23">
+        <v>83.13770877777779</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24">
+        <v>21.99799683333334</v>
+      </c>
+      <c r="G24">
+        <v>83.13708583333334</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>21.99799683333334</v>
+      </c>
+      <c r="G25">
+        <v>83.13708583333334</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <v>21.99795758333333</v>
+      </c>
+      <c r="G26">
+        <v>83.13636416666667</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <v>21.99793183333334</v>
+      </c>
+      <c r="G27">
+        <v>83.13562911111111</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>24</v>
       </c>
-      <c r="I3" t="s">
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <v>21.99730761111111</v>
+      </c>
+      <c r="G28">
+        <v>83.12554677777777</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29">
+        <v>21.99730761111111</v>
+      </c>
+      <c r="G29">
+        <v>83.12554677777777</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30">
+        <v>21.99625616666667</v>
+      </c>
+      <c r="G30">
+        <v>83.12110808333333</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>26</v>
       </c>
-      <c r="J3">
-        <v>32.04</v>
-      </c>
-      <c r="K3">
-        <v>7.810000000000002</v>
-      </c>
-      <c r="L3">
-        <v>28.14</v>
-      </c>
-      <c r="M3">
-        <v>35.95</v>
-      </c>
-      <c r="N3">
-        <v>25.09508463888889</v>
-      </c>
-      <c r="O3">
-        <v>82.35395769444443</v>
-      </c>
-      <c r="P3" s="2" t="s">
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31">
+        <v>21.99618344444444</v>
+      </c>
+      <c r="G31">
+        <v>83.12031938888889</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32">
+        <v>21.99618344444444</v>
+      </c>
+      <c r="G32">
+        <v>83.12031938888889</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33">
+        <v>21.99612047222222</v>
+      </c>
+      <c r="G33">
+        <v>83.12044580555555</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34">
+        <v>21.99594452777778</v>
+      </c>
+      <c r="G34">
+        <v>83.11980966666665</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>28</v>
       </c>
-      <c r="R3" t="s">
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>21.9975935</v>
+      </c>
+      <c r="G35">
+        <v>83.12795558333333</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36">
+        <v>21.99741552777778</v>
+      </c>
+      <c r="G36">
+        <v>83.12618497222222</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
         <v>30</v>
       </c>
-      <c r="S3" t="s">
-        <v>24</v>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37">
+        <v>21.99431733333333</v>
+      </c>
+      <c r="G37">
+        <v>83.11292483333332</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38">
+        <v>21.99377316666667</v>
+      </c>
+      <c r="G38">
+        <v>83.11060877777777</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39">
+        <v>21.99377316666667</v>
+      </c>
+      <c r="G39">
+        <v>83.11060877777777</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40">
+        <v>21.99366305555556</v>
+      </c>
+      <c r="G40">
+        <v>83.10997547222222</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41">
+        <v>21.99546566666667</v>
+      </c>
+      <c r="G41">
+        <v>83.11770697222221</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42">
+        <v>21.99546566666667</v>
+      </c>
+      <c r="G42">
+        <v>83.11770697222221</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43">
+        <v>21.99530119444444</v>
+      </c>
+      <c r="G43">
+        <v>83.11699483333332</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44">
+        <v>21.99530119444444</v>
+      </c>
+      <c r="G44">
+        <v>83.11699483333332</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45">
+        <v>21.99515019444445</v>
+      </c>
+      <c r="G45">
+        <v>83.11634863888888</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="P2" r:id="rId1"/>
-    <hyperlink ref="Q2" r:id="rId2"/>
-    <hyperlink ref="P3" r:id="rId3"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
